--- a/excel_report/BaoCao_Register_Cart.xlsx
+++ b/excel_report/BaoCao_Register_Cart.xlsx
@@ -146,13 +146,16 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -168,9 +171,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BAO CAO KIEM THU - MODULE DANG KY (REGISTER) - mhm.vn</t>
+          <t>BÁO CÁO KIỂM THỬ - MODULE ĐĂNG KÝ (REGISTER) - mhm.vn</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Mo trang dang ky va hien thi form</t>
+          <t>Để trống toàn bộ các trường bắt buộc</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Mo trang /account/register</t>
+          <t>Tất cả trường rỗng</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>URL la /account/register, hien thi form dang ky va nut submit</t>
+          <t>Hiển thị validation cho tất cả trường bắt buộc</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -631,17 +631,17 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Khong dien thong tin nao</t>
+          <t>Chỉ trường Họ để trống, các trường còn lại hợp lệ</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Tat ca truong rong</t>
+          <t>LastName = rỗng</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Hien thi validation cho tat ca truong bat buoc</t>
+          <t>Hiển thị validation trường Họ</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -663,17 +663,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Khong dien ho</t>
+          <t>Chỉ trường Tên để trống, các trường còn lại hợp lệ</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>LastName = rong</t>
+          <t>FirstName = rỗng</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Hien thi validation truong Ho</t>
+          <t>Hiển thị validation trường Tên</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -695,17 +695,17 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Khong dien ten</t>
+          <t>Chỉ trường Số điện thoại để trống, các trường còn lại hợp lệ</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>FirstName = rong</t>
+          <t>Phone = rỗng</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Hien thi validation truong Ten</t>
+          <t>Hiển thị validation trường Số điện thoại</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -727,17 +727,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Khong dien so dien thoai</t>
+          <t>Số điện thoại chứa ký tự chữ, các trường còn lại hợp lệ</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Phone = rong</t>
+          <t>09ab123</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Hien thi validation truong So dien thoai</t>
+          <t>Hiển thị validation số điện thoại không hợp lệ</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -759,17 +759,17 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Khong dien email</t>
+          <t>Chỉ trường Email để trống, các trường còn lại hợp lệ</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Email = rong</t>
+          <t>Email = rỗng</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Hien thi validation truong Email</t>
+          <t>Hiển thị validation Email</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Khong dien mat khau</t>
+          <t>Email sai định dạng, các trường còn lại hợp lệ</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Password = rong</t>
+          <t>abc@</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Hien thi validation truong Mat khau</t>
+          <t>Hiển thị validation Email không hợp lệ</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -823,17 +823,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>So dien thoai chua chu cai</t>
+          <t>Email có khoảng trắng ở đầu, các trường còn lại hợp lệ</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Phone = 09ab123456</t>
+          <t>" test111@gmail.com"</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Hien thi validation so dien thoai khong hop le</t>
+          <t>Đăng ký thành công</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -855,17 +855,17 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>So dien thoai chua ky tu dac biet</t>
+          <t>Email có khoảng trắng ở cuối, các trường còn lại hợp lệ</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Phone = 0900-123-456</t>
+          <t>"test111@gmail.com "</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Hien thi validation so dien thoai khong hop le</t>
+          <t>Đăng ký thành công</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -887,17 +887,17 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Email sai dinh dang "abc@"</t>
+          <t>Chỉ trường Mật khẩu để trống, các trường còn lại hợp lệ</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Email = abc@</t>
+          <t>Password = rỗng</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Hien thi validation email khong hop le</t>
+          <t>Hiển thị validation Mật khẩu</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -919,17 +919,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Email khong co ky tu @</t>
+          <t>Mật khẩu có chữ hoa và số, các trường còn lại hợp lệ</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Email = abcexample.com</t>
+          <t>Abc12345</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Hien thi validation email khong hop le</t>
+          <t>Đăng ký thành công</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Email co dau cham o cuoi ten mien</t>
+          <t>Mật khẩu chỉ có 1 ký tự, các trường còn lại hợp lệ</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Email = abc@example.</t>
+          <t>a</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Hien thi validation email khong hop le</t>
+          <t>Hiển thị thông báo mật khẩu quá ngắn</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -983,17 +983,17 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Email co khoang trang o dau duoc browser trim</t>
+          <t>Mật khẩu chứa ký tự đặc biệt, các trường còn lại hợp lệ</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Email = '  email@example.com'</t>
+          <t>Test@123!</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Browser tu trim khoang trang dau, email khong con khoang trang</t>
+          <t>Đăng ký thành công</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Email co khoang trang o cuoi duoc browser trim</t>
+          <t>Mật khẩu vượt quá độ dài cho phép (256 ký tự), các trường còn lại hợp lệ</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Email = 'email@example.com  '</t>
+          <t>Password 256 ký tự</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Browser tu trim khoang trang cuoi, email khong con khoang trang</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>Hiển thị lỗi mật khẩu quá dài</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1047,20 +1047,20 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Ho chi chua khoang trang phai bi validate</t>
+          <t>Họ là số và các trường còn lại hợp lệ</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>LastName = '   '</t>
+          <t>LastName = 12345</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Hien thi loi Ho khong hop le / khong duoc de trong</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
+          <t>Hiển thị lỗi họ không hợp lệ</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -1079,20 +1079,20 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Ten chi chua khoang trang phai bi validate</t>
+          <t>Tên là số và các trường còn lại hợp lệ</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>FirstName = '   '</t>
+          <t>FirstName = 67890</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Hien thi loi Ten khong hop le / khong duoc de trong</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
+          <t>Hiển thị lỗi tên không hợp lệ</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -1111,20 +1111,20 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Ho la so phai bi validate</t>
+          <t>Họ chỉ chứa khoảng trắng và các trường còn lại hợp lệ</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>LastName = 12345</t>
+          <t>LastName = " "</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Hien thi loi Ho khong hop le</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
+          <t>Hiển thị lỗi họ không được để trống</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -1143,20 +1143,20 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Ten la so phai bi validate</t>
+          <t>Tên chỉ chứa khoảng trắng và các trường còn lại hợp lệ</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>FirstName = 67890</t>
+          <t>FirstName = " "</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Hien thi loi Ten khong hop le</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
+          <t>Hiển thị lỗi tên không được để trống</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -1175,27 +1175,27 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Mat khau 1 ky tu phai bi validate do qua ngan</t>
+          <t>Đăng ký với toàn bộ thông tin hợp lệ</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Password = a</t>
+          <t>Dữ liệu hợp lệ</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Hien thi loi mat khau qua ngan</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Đăng ký thành công</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Khong lo loi he thong khi validate form dang ky</t>
+          <t>Đăng ký bằng email đã tồn tại trong hệ thống</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Email = abc@ roi submit</t>
+          <t>Email đã đăng ký</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Khong hien thi [object Object] / undefined / null / Liquid error</t>
+          <t>Hiển thị thông báo email đã tồn tại</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -1231,39 +1231,359 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>TC_REGISTER_021</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Họ và Tên vượt quá độ dài cho phép (300 ký tự), các trường còn lại hợp lệ</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>LastName=300 ký tự, FirstName=300 ký tự</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Hiển thị thông báo họ/tên quá dài</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>TC_REGISTER_022</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Mật khẩu vượt quá độ dài cho phép (300 ký tự), các trường còn lại hợp lệ</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Password=300 ký tự</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Hiển thị thông báo mật khẩu quá dài</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>TC_REGISTER_023</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Số điện thoại đã tồn tại trong hệ thống, các trường còn lại hợp lệ</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Phone đã đăng ký</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Hiển thị thông báo số điện thoại đã tồn tại</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>TC_REGISTER_024</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Họ chứa ký tự đặc biệt và các trường còn lại hợp lệ</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Nguyen@#$</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Hiển thị lỗi họ không hợp lệ</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>TC_REGISTER_025</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Tên chứa ký tự đặc biệt và các trường còn lại hợp lệ</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>An@#$</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Hiển thị lỗi tên không hợp lệ</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>TC_REGISTER_026</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Số điện thoại ngắn hơn độ dài tối thiểu và các trường còn lại hợp lệ</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>09123</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Hiển thị lỗi số điện thoại không hợp lệ</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>TC_REGISTER_027</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Số điện thoại dài hơn độ dài tối đa và các trường còn lại hợp lệ</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>0282818221821291234567890123</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Hiển thị lỗi số điện thoại không hợp lệ</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>TC_REGISTER_028</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Email vượt quá độ dài cho phép và các trường còn lại hợp lệ</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Email &gt; 255 ký tự</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Hiển thị lỗi email quá dài</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>TC_REGISTER_029</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Chèn mã XSS vào trường Họ/Tên và các trường còn lại hợp lệ</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>&lt;script&gt;alert(1)&lt;/script&gt;</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Không thực thi script, hiển thị lỗi tên không hợp lệ</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>TC_REGISTER_030</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Nhấn nút Đăng ký liên tục 2 lần với dữ liệu hợp lệ</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Double Click Submit</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Chỉ tạo 1 tài khoản duy nhất</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>Tong so test case</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>15/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>5/20</t>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1615,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BAO CAO KIEM THU - MODULE GIO HANG (CART) - mhm.vn</t>
+          <t>BÁO CÁO KIỂM THỬ - MODULE GIỎ HÀNG (CART) - mhm.vn</t>
         </is>
       </c>
     </row>
@@ -1339,17 +1659,17 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Mo trang gio hang khi chua co san pham</t>
+          <t>Mở trang giỏ hàng khi chưa có sản phẩm</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Mo /cart khi gio rong</t>
+          <t>Giỏ hàng rỗng</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>URL la /cart, gio rong, hien thi thong bao gio hang trong</t>
+          <t>URL là /cart, giỏ rỗng, hiển thị thông báo giỏ hàng trống</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -1371,17 +1691,17 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Tu trang chu click icon gio hang</t>
+          <t>Từ trang chủ click icon giỏ hàng</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Click icon gio hang o trang chu</t>
+          <t>Click icon giỏ hàng</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Dieu huong den trang /cart</t>
+          <t>Điều hướng đến trang /cart</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -1403,17 +1723,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Them san pham vao gio hang bang endpoint add.js</t>
+          <t>Thêm sản phẩm bằng endpoint add.js</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>variantId, quantity = 1</t>
+          <t>iPhone 17 Pro Max, SL=1</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Response ok, item_count = 1, dung ten san pham</t>
+          <t>Response ok, item_count = 1, đúng tên sản phẩm</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -1435,17 +1755,17 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Gio hang hien thi san pham da them</t>
+          <t>Giỏ hàng hiển thị sản phẩm đã thêm</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Them SP quantity = 1, mo gio</t>
+          <t>iPhone 17 Pro Max, SL=1</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Gio co san pham, item_count = 1, dung ten san pham</t>
+          <t>Giỏ có sản phẩm, item_count = 1, đúng tên sản phẩm</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -1467,17 +1787,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Them san pham voi so luong 2</t>
+          <t>Thêm sản phẩm với số lượng 2</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>quantity = 2</t>
+          <t>iPhone 17 Pro Max, SL=2</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Input so luong = 2, item_count = 2</t>
+          <t>Input số lượng = 2, item_count = 2</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1499,17 +1819,17 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Them cung mot san pham 2 lan thi cong don so luong</t>
+          <t>Thêm cùng một sản phẩm 2 lần thì cộng dồn số lượng</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Them quantity = 1 hai lan</t>
+          <t>Add SL=1 hai lần</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>item_count = 2, quantity gop = 2</t>
+          <t>item_count = 2, quantity gộp = 2</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -1531,17 +1851,17 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Nut tang so luong tren UI lam tang gia tri input</t>
+          <t>Nút tăng số lượng trên UI làm tăng giá trị input</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Click nut + tren item dau</t>
+          <t>Click nút + trên item đầu</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Gia tri input so luong = 2</t>
+          <t>Giá trị input số lượng = 2</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1563,17 +1883,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Nut giam so luong tren UI khong cho giam duoi 1</t>
+          <t>Nút giảm số lượng trên UI không cho giảm dưới 1</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Click nut - khi so luong = 1</t>
+          <t>Click nút - khi SL=1</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>So luong van giu = 1</t>
+          <t>Số lượng vẫn giữ = 1</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -1595,12 +1915,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Cap nhat so luong ve 3 bang endpoint change.js</t>
+          <t>Cập nhật số lượng về 3 bằng endpoint change.js</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>change quantity = 3</t>
+          <t>change SL=3</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1627,12 +1947,12 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Cap nhat so luong ve 0 de xoa san pham</t>
+          <t>Cập nhật số lượng về 0 để xóa sản phẩm</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>change quantity = 0</t>
+          <t>change SL=0</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -1659,17 +1979,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Nut tiep tuc mua hang tren gio hang rong quay ve trang chu</t>
+          <t>Tiếp tục mua hàng từ giỏ hàng rỗng quay về trang chủ</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Click nut 'Tiep tuc mua hang'</t>
+          <t>Click nút Tiếp tục mua hàng</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Dieu huong ve https://mhm.vn/</t>
+          <t>Điều hướng về https://mhm.vn/</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1691,17 +2011,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Gio hang co san pham hien thi tong tien</t>
+          <t>Giỏ hàng có sản phẩm hiển thị tổng tiền</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Them SP, mo gio</t>
+          <t>Có sản phẩm trong giỏ</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Hien thi tong tien co chu so va ky hieu d</t>
+          <t>Hiển thị tổng tiền có chữ số và ký hiệu ₫</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -1723,17 +2043,17 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Gio hang co san pham hien thi nut thanh toan</t>
+          <t>Giỏ hàng có sản phẩm hiển thị nút thanh toán</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Them SP, mo gio</t>
+          <t>Có sản phẩm trong giỏ</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Hien thi nut thanh toan</t>
+          <t>Hiển thị nút Thanh toán</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1755,17 +2075,17 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Reload trang gio hang van giu san pham</t>
+          <t>Reload trang giỏ hàng vẫn giữ sản phẩm</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Them SP, reload trang</t>
+          <t>Reload trang giỏ hàng</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Van giu san pham va dung ten san pham</t>
+          <t>Vẫn giữ sản phẩm và đúng tên sản phẩm</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -1787,17 +2107,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Khong hien thi loi he thong tren trang gio hang</t>
+          <t>Không hiển thị lỗi hệ thống trên trang giỏ hàng</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Them SP, mo gio</t>
+          <t>Có sản phẩm trong giỏ</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Khong hien thi [object Object] / undefined / null / Liquid error</t>
+          <t>Không hiển thị [object Object] / undefined / null / Liquid error</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -1819,25 +2139,25 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Tang so luong tren UI phai dong bo vao gio hang server</t>
+          <t>Tăng số lượng trên UI phải đồng bộ vào giỏ hàng server</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Click nut + roi doc cart.js</t>
+          <t>Click nút + rồi đọc cart.js</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>item_count = 2 dong bo voi server</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
+          <t>item_count = 2 đồng bộ với server</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>Flaky</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -1851,27 +2171,27 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Nut thanh toan phai dieu huong truc tiep den checkout</t>
+          <t>Nút thanh toán phải điều hướng trực tiếp đến checkout</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Kiem tra thuoc tinh href cua nut thanh toan</t>
+          <t>Kiểm tra thuộc tính href của nút thanh toán</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Nut thanh toan co href chua /checkout</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
+          <t>Nút thanh toán có href chứa /checkout</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1883,20 +2203,20 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>O so luong phai co ten truy cap ro rang</t>
+          <t>Ô số lượng có tên truy cập rõ ràng cho Screen Reader</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Kiem tra accessible name cua input so luong</t>
+          <t>Kiểm tra accessible name của input số lượng</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Input co aria-label / label 'So luong' cho screen reader</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
+          <t>Input có aria-label / label 'Số lượng' cho screen reader</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -1907,44 +2227,44 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>Tong so test case</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>15/18</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>2/18</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Flaky</t>
         </is>
